--- a/artfynd/A 34099-2025 artfynd.xlsx
+++ b/artfynd/A 34099-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74247169</v>
       </c>
       <c r="B2" t="n">
-        <v>96953</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99242</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>445792.7750803341</v>
+        <v>445793</v>
       </c>
       <c r="R2" t="n">
-        <v>6360806.23281298</v>
+        <v>6360806</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1987-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1987-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 34099-2025 artfynd.xlsx
+++ b/artfynd/A 34099-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74247169</v>
       </c>
       <c r="B2" t="n">
-        <v>99242</v>
+        <v>99247</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34099-2025 artfynd.xlsx
+++ b/artfynd/A 34099-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74247169</v>
       </c>
       <c r="B2" t="n">
-        <v>99247</v>
+        <v>99248</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34099-2025 artfynd.xlsx
+++ b/artfynd/A 34099-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74247169</v>
       </c>
       <c r="B2" t="n">
-        <v>99248</v>
+        <v>99275</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34099-2025 artfynd.xlsx
+++ b/artfynd/A 34099-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74247169</v>
       </c>
       <c r="B2" t="n">
-        <v>99275</v>
+        <v>99281</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34099-2025 artfynd.xlsx
+++ b/artfynd/A 34099-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74247169</v>
       </c>
       <c r="B2" t="n">
-        <v>99281</v>
+        <v>99288</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34099-2025 artfynd.xlsx
+++ b/artfynd/A 34099-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74247169</v>
       </c>
       <c r="B2" t="n">
-        <v>99288</v>
+        <v>99292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34099-2025 artfynd.xlsx
+++ b/artfynd/A 34099-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74247169</v>
       </c>
       <c r="B2" t="n">
-        <v>99292</v>
+        <v>99299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34099-2025 artfynd.xlsx
+++ b/artfynd/A 34099-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74247169</v>
       </c>
       <c r="B2" t="n">
-        <v>99302</v>
+        <v>99307</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34099-2025 artfynd.xlsx
+++ b/artfynd/A 34099-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74247169</v>
       </c>
       <c r="B2" t="n">
-        <v>99307</v>
+        <v>99315</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34099-2025 artfynd.xlsx
+++ b/artfynd/A 34099-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74247169</v>
       </c>
       <c r="B2" t="n">
-        <v>99315</v>
+        <v>99325</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
